--- a/2026年下半年减肥记录每一天.xlsx
+++ b/2026年下半年减肥记录每一天.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="46">
   <si>
     <t>时间</t>
   </si>
@@ -150,6 +150,31 @@
   </si>
   <si>
     <t>比较满意，生活化</t>
+  </si>
+  <si>
+    <t>2026-9-10 周四</t>
+  </si>
+  <si>
+    <t>西红柿1  + 小玉米1 + 鸡蛋2</t>
+  </si>
+  <si>
+    <t>小玉米1</t>
+  </si>
+  <si>
+    <t>西红柿1</t>
+  </si>
+  <si>
+    <t>目前82.6kg
+本周争取到82.3kg，加油</t>
+  </si>
+  <si>
+    <t>猪排 豆腐 凉拌黄瓜套餐</t>
+  </si>
+  <si>
+    <t>猪排 豆腐</t>
+  </si>
+  <si>
+    <t>黄瓜 + 莲白</t>
   </si>
 </sst>
 </file>
@@ -1318,27 +1343,55 @@
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="6"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="A11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="4"/>
+      <c r="A13" s="6"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>

--- a/2026年下半年减肥记录每一天.xlsx
+++ b/2026年下半年减肥记录每一天.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="51">
   <si>
     <t>时间</t>
   </si>
@@ -175,6 +175,22 @@
   </si>
   <si>
     <t>黄瓜 + 莲白</t>
+  </si>
+  <si>
+    <t>2026-10-09 周五</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>满意，生活化，蛋白质缺乏</t>
+  </si>
+  <si>
+    <t>目前84.5kg
+本周争取到84kg，加油</t>
+  </si>
+  <si>
+    <t>三木桔健康餐</t>
   </si>
 </sst>
 </file>
@@ -1431,19 +1447,37 @@
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="6"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="A17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="4"/>
+      <c r="A18" s="6"/>
       <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
+      <c r="C18" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -1451,7 +1485,7 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="4"/>
+      <c r="A19" s="6"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>

--- a/2026年下半年减肥记录每一天.xlsx
+++ b/2026年下半年减肥记录每一天.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
   <si>
     <t>时间</t>
   </si>
@@ -191,6 +191,25 @@
   </si>
   <si>
     <t>三木桔健康餐</t>
+  </si>
+  <si>
+    <t>荞麦面 + 白菜 + 牛肉</t>
+  </si>
+  <si>
+    <t>2026-10-14 周三</t>
+  </si>
+  <si>
+    <t>西红柿1 + 玉米馒头 + 鸡蛋2</t>
+  </si>
+  <si>
+    <t>玉米馒头</t>
+  </si>
+  <si>
+    <t>满意，生活化，蔬菜缺一点</t>
+  </si>
+  <si>
+    <t>目前84.45kg
+本周争取到84kg，加油</t>
   </si>
 </sst>
 </file>
@@ -1474,7 +1493,9 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="6"/>
-      <c r="B18" s="4"/>
+      <c r="B18" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="C18" s="4" t="s">
         <v>50</v>
       </c>
@@ -1486,8 +1507,12 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="6"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
+      <c r="B19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -1495,27 +1520,43 @@
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="6"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="5"/>
+      <c r="A20" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="4"/>
+      <c r="A21" s="6"/>
       <c r="B21" s="4"/>
-      <c r="C21" s="5"/>
+      <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="5"/>
+      <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="4"/>
+      <c r="A22" s="6"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>

--- a/2026年下半年减肥记录每一天.xlsx
+++ b/2026年下半年减肥记录每一天.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="68">
   <si>
     <t>时间</t>
   </si>
@@ -210,6 +210,40 @@
   <si>
     <t>目前84.45kg
 本周争取到84kg，加油</t>
+  </si>
+  <si>
+    <t>2026-10-19周一</t>
+  </si>
+  <si>
+    <t>黄瓜1 + 白馒头 + 鸡蛋2</t>
+  </si>
+  <si>
+    <t>白馒头</t>
+  </si>
+  <si>
+    <t>黄瓜1</t>
+  </si>
+  <si>
+    <t>很满意，生活化</t>
+  </si>
+  <si>
+    <t>目前84.35kg
+本周争取到82kg，加油</t>
+  </si>
+  <si>
+    <t>饺子(5个韭菜鸡蛋 + 5个芹菜猪肉)</t>
+  </si>
+  <si>
+    <t>鸡蛋 + 猪肉</t>
+  </si>
+  <si>
+    <t>饺子皮</t>
+  </si>
+  <si>
+    <t>韭菜 + 芹菜</t>
+  </si>
+  <si>
+    <t>荞麦面 + 白菜 + 鸡蛋</t>
   </si>
 </sst>
 </file>
@@ -1566,29 +1600,61 @@
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="6"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="5"/>
+      <c r="A23" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>67</v>
+      </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>

--- a/2026年下半年减肥记录每一天.xlsx
+++ b/2026年下半年减肥记录每一天.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
   <si>
     <t>时间</t>
   </si>
@@ -243,7 +243,42 @@
     <t>韭菜 + 芹菜</t>
   </si>
   <si>
-    <t>荞麦面 + 白菜 + 鸡蛋</t>
+    <t>全麦饼 + 午餐肉 + 鸡蛋 + 菠菜 + 一点蛋糕</t>
+  </si>
+  <si>
+    <t>鸡蛋 + 午餐肉</t>
+  </si>
+  <si>
+    <t>全麦饼</t>
+  </si>
+  <si>
+    <t>菠菜</t>
+  </si>
+  <si>
+    <t>还行，吃了点蛋糕</t>
+  </si>
+  <si>
+    <t>小白菜 + 鸡蛋2 + 半截玉米</t>
+  </si>
+  <si>
+    <t>半截玉米</t>
+  </si>
+  <si>
+    <t>小白菜</t>
+  </si>
+  <si>
+    <t>目前84.10kg
+明天争取到83.6kg，加油</t>
+  </si>
+  <si>
+    <t>韭菜盒子 + 西红柿鸡蛋汤</t>
+  </si>
+  <si>
+    <t>西红柿1 + 白馒头 + 鸡蛋2</t>
+  </si>
+  <si>
+    <t>目前84.25kg
+明天争取到83.6kg，加油</t>
   </si>
 </sst>
 </file>
@@ -1655,56 +1690,107 @@
       <c r="C25" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
+      <c r="D25" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="6"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="5"/>
+      <c r="A26" s="3">
+        <v>46315</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>76</v>
+      </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="6"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="5"/>
+      <c r="A29" s="3">
+        <v>46315</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
+      <c r="A30" s="6"/>
+      <c r="B30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -1712,13 +1798,15 @@
       <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="5"/>
+      <c r="A31" s="6"/>
+      <c r="B31" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
+      <c r="G31" s="1"/>
       <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8">

--- a/2026年下半年减肥记录每一天.xlsx
+++ b/2026年下半年减肥记录每一天.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="84">
   <si>
     <t>时间</t>
   </si>
@@ -278,6 +278,22 @@
   </si>
   <si>
     <t>目前84.25kg
+明天争取到83.6kg，加油</t>
+  </si>
+  <si>
+    <t>杂粮饭</t>
+  </si>
+  <si>
+    <t>混合蔬菜</t>
+  </si>
+  <si>
+    <t>抄手 + 豆腐 + 豌豆</t>
+  </si>
+  <si>
+    <t>继续加油，缺少蔬菜</t>
+  </si>
+  <si>
+    <t>目前83.75kg
 明天争取到83.6kg，加油</t>
   </si>
 </sst>
@@ -1240,7 +1256,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="18.75" style="1" customWidth="1"/>
@@ -1759,7 +1775,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="3">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>9</v>
@@ -1791,10 +1807,18 @@
       <c r="C30" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
+      <c r="D30" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8">
@@ -1802,27 +1826,51 @@
       <c r="B31" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C31" s="4"/>
+      <c r="C31" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
-      <c r="G31" s="1"/>
+      <c r="G31" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="6"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="5"/>
+      <c r="A32" s="3">
+        <v>46317</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="5"/>
+      <c r="A33" s="6"/>
+      <c r="B33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -1830,19 +1878,23 @@
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="5"/>
+      <c r="A34" s="6"/>
+      <c r="B34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
+      <c r="G34" s="1"/>
       <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
+      <c r="A35" s="3">
+        <v>46318</v>
+      </c>
       <c r="B35" s="4"/>
-      <c r="C35" s="5"/>
+      <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
@@ -1850,9 +1902,9 @@
       <c r="H35" s="5"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="4"/>
+      <c r="A36" s="6"/>
       <c r="B36" s="4"/>
-      <c r="C36" s="5"/>
+      <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
@@ -1860,17 +1912,19 @@
       <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="4"/>
+      <c r="A37" s="6"/>
       <c r="B37" s="4"/>
-      <c r="C37" s="5"/>
+      <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
+      <c r="G37" s="1"/>
       <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
+      <c r="A38" s="3">
+        <v>46321</v>
+      </c>
       <c r="B38" s="4"/>
       <c r="C38" s="5"/>
       <c r="D38" s="4"/>
@@ -1880,7 +1934,7 @@
       <c r="H38" s="5"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="4"/>
+      <c r="A39" s="6"/>
       <c r="B39" s="4"/>
       <c r="C39" s="5"/>
       <c r="D39" s="4"/>
@@ -1890,7 +1944,7 @@
       <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="4"/>
+      <c r="A40" s="6"/>
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
       <c r="D40" s="4"/>
@@ -1900,7 +1954,9 @@
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="6"/>
+      <c r="A41" s="3">
+        <v>46322</v>
+      </c>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
       <c r="D41" s="4"/>
@@ -1917,10 +1973,10 @@
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
-      <c r="H42" s="5"/>
+      <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="4"/>
+      <c r="A43" s="6"/>
       <c r="B43" s="4"/>
       <c r="C43" s="5"/>
       <c r="D43" s="4"/>
@@ -1930,14 +1986,16 @@
       <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="4"/>
+      <c r="A44" s="3">
+        <v>46323</v>
+      </c>
       <c r="B44" s="4"/>
       <c r="C44" s="5"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
+      <c r="H44" s="5"/>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="6"/>
@@ -1947,10 +2005,10 @@
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
-      <c r="H45" s="5"/>
+      <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="4"/>
+      <c r="A46" s="6"/>
       <c r="B46" s="4"/>
       <c r="C46" s="5"/>
       <c r="D46" s="4"/>
@@ -1960,24 +2018,24 @@
       <c r="H46" s="4"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="4"/>
+      <c r="A47" s="6"/>
       <c r="B47" s="4"/>
       <c r="C47" s="5"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
+      <c r="H47" s="5"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="6"/>
+      <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="5"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
-      <c r="H48" s="5"/>
+      <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="4"/>
@@ -1990,24 +2048,24 @@
       <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="4"/>
+      <c r="A50" s="6"/>
       <c r="B50" s="4"/>
       <c r="C50" s="5"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
+      <c r="H50" s="5"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="6"/>
+      <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="5"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
-      <c r="H51" s="5"/>
+      <c r="H51" s="4"/>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="4"/>
@@ -2020,24 +2078,24 @@
       <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="4"/>
+      <c r="A53" s="6"/>
       <c r="B53" s="4"/>
       <c r="C53" s="5"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
+      <c r="H53" s="5"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="6"/>
+      <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="5"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
-      <c r="H54" s="5"/>
+      <c r="H54" s="4"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="4"/>
@@ -2050,24 +2108,24 @@
       <c r="H55" s="4"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="4"/>
+      <c r="A56" s="6"/>
       <c r="B56" s="4"/>
       <c r="C56" s="5"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
+      <c r="H56" s="5"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="6"/>
+      <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="5"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
-      <c r="H57" s="5"/>
+      <c r="H57" s="4"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="4"/>
@@ -2080,24 +2138,24 @@
       <c r="H58" s="4"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="4"/>
+      <c r="A59" s="6"/>
       <c r="B59" s="4"/>
       <c r="C59" s="5"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
       <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
+      <c r="H59" s="5"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="6"/>
+      <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="5"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
-      <c r="H60" s="5"/>
+      <c r="H60" s="4"/>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="4"/>
@@ -2110,24 +2168,24 @@
       <c r="H61" s="4"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="4"/>
+      <c r="A62" s="6"/>
       <c r="B62" s="4"/>
       <c r="C62" s="5"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
+      <c r="H62" s="5"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="6"/>
+      <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="5"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
-      <c r="H63" s="5"/>
+      <c r="H63" s="4"/>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="4"/>
@@ -2140,24 +2198,24 @@
       <c r="H64" s="4"/>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="4"/>
+      <c r="A65" s="6"/>
       <c r="B65" s="4"/>
       <c r="C65" s="5"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
+      <c r="H65" s="5"/>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="6"/>
+      <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="5"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
-      <c r="H66" s="5"/>
+      <c r="H66" s="4"/>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="4"/>
@@ -2170,24 +2228,24 @@
       <c r="H67" s="4"/>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="4"/>
+      <c r="A68" s="6"/>
       <c r="B68" s="4"/>
       <c r="C68" s="5"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
+      <c r="H68" s="5"/>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="6"/>
+      <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="5"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
-      <c r="H69" s="5"/>
+      <c r="H69" s="4"/>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="4"/>
@@ -2200,24 +2258,24 @@
       <c r="H70" s="4"/>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="4"/>
+      <c r="A71" s="6"/>
       <c r="B71" s="4"/>
       <c r="C71" s="5"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
+      <c r="H71" s="5"/>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="6"/>
+      <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="5"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
       <c r="G72" s="4"/>
-      <c r="H72" s="5"/>
+      <c r="H72" s="4"/>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="4"/>
@@ -2230,24 +2288,24 @@
       <c r="H73" s="4"/>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="4"/>
+      <c r="A74" s="6"/>
       <c r="B74" s="4"/>
       <c r="C74" s="5"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
       <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
+      <c r="H74" s="5"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="6"/>
+      <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="5"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
       <c r="G75" s="4"/>
-      <c r="H75" s="5"/>
+      <c r="H75" s="4"/>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="4"/>
@@ -2260,24 +2318,24 @@
       <c r="H76" s="4"/>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="4"/>
+      <c r="A77" s="6"/>
       <c r="B77" s="4"/>
       <c r="C77" s="5"/>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
+      <c r="H77" s="5"/>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="6"/>
+      <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="5"/>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
-      <c r="H78" s="5"/>
+      <c r="H78" s="4"/>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="4"/>
@@ -2290,24 +2348,24 @@
       <c r="H79" s="4"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="4"/>
+      <c r="A80" s="6"/>
       <c r="B80" s="4"/>
       <c r="C80" s="5"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
+      <c r="H80" s="5"/>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="6"/>
+      <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="5"/>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
-      <c r="H81" s="5"/>
+      <c r="H81" s="4"/>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="4"/>
@@ -2320,24 +2378,24 @@
       <c r="H82" s="4"/>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" s="4"/>
+      <c r="A83" s="6"/>
       <c r="B83" s="4"/>
       <c r="C83" s="5"/>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
       <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
+      <c r="H83" s="5"/>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="6"/>
+      <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="5"/>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
       <c r="F84" s="4"/>
       <c r="G84" s="4"/>
-      <c r="H84" s="5"/>
+      <c r="H84" s="4"/>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="4"/>
@@ -2350,24 +2408,24 @@
       <c r="H85" s="4"/>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="4"/>
+      <c r="A86" s="6"/>
       <c r="B86" s="4"/>
       <c r="C86" s="5"/>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
-      <c r="H86" s="4"/>
+      <c r="H86" s="5"/>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="6"/>
+      <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="5"/>
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
-      <c r="H87" s="5"/>
+      <c r="H87" s="4"/>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="4"/>
@@ -2380,24 +2438,24 @@
       <c r="H88" s="4"/>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="4"/>
+      <c r="A89" s="6"/>
       <c r="B89" s="4"/>
       <c r="C89" s="5"/>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
       <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
+      <c r="H89" s="5"/>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="6"/>
+      <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="5"/>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
       <c r="F90" s="4"/>
       <c r="G90" s="4"/>
-      <c r="H90" s="5"/>
+      <c r="H90" s="4"/>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="4"/>
@@ -2410,24 +2468,24 @@
       <c r="H91" s="4"/>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="4"/>
+      <c r="A92" s="6"/>
       <c r="B92" s="4"/>
       <c r="C92" s="5"/>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
       <c r="F92" s="4"/>
       <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
+      <c r="H92" s="5"/>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="6"/>
+      <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="5"/>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
       <c r="G93" s="4"/>
-      <c r="H93" s="5"/>
+      <c r="H93" s="4"/>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="4"/>
@@ -2440,24 +2498,24 @@
       <c r="H94" s="4"/>
     </row>
     <row r="95" spans="1:8">
-      <c r="A95" s="4"/>
+      <c r="A95" s="6"/>
       <c r="B95" s="4"/>
       <c r="C95" s="5"/>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
+      <c r="H95" s="5"/>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="6"/>
+      <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="5"/>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
       <c r="G96" s="4"/>
-      <c r="H96" s="5"/>
+      <c r="H96" s="4"/>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="4"/>
@@ -2470,24 +2528,24 @@
       <c r="H97" s="4"/>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="4"/>
+      <c r="A98" s="6"/>
       <c r="B98" s="4"/>
       <c r="C98" s="5"/>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
-      <c r="H98" s="4"/>
+      <c r="H98" s="5"/>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="6"/>
+      <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="5"/>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
-      <c r="H99" s="5"/>
+      <c r="H99" s="4"/>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="4"/>
@@ -2500,24 +2558,24 @@
       <c r="H100" s="4"/>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="4"/>
+      <c r="A101" s="6"/>
       <c r="B101" s="4"/>
       <c r="C101" s="5"/>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
-      <c r="H101" s="4"/>
+      <c r="H101" s="5"/>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="6"/>
+      <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="5"/>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
       <c r="G102" s="4"/>
-      <c r="H102" s="5"/>
+      <c r="H102" s="4"/>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="4"/>
@@ -2530,24 +2588,24 @@
       <c r="H103" s="4"/>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" s="4"/>
+      <c r="A104" s="6"/>
       <c r="B104" s="4"/>
       <c r="C104" s="5"/>
       <c r="D104" s="4"/>
       <c r="E104" s="4"/>
       <c r="F104" s="4"/>
       <c r="G104" s="4"/>
-      <c r="H104" s="4"/>
+      <c r="H104" s="5"/>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="6"/>
+      <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="5"/>
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
       <c r="G105" s="4"/>
-      <c r="H105" s="5"/>
+      <c r="H105" s="4"/>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="4"/>
@@ -2556,28 +2614,28 @@
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
-      <c r="G106" s="4"/>
+      <c r="G106" s="5"/>
       <c r="H106" s="4"/>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" s="4"/>
+      <c r="A107" s="6"/>
       <c r="B107" s="4"/>
       <c r="C107" s="5"/>
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
-      <c r="G107" s="5"/>
-      <c r="H107" s="4"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="5"/>
     </row>
     <row r="108" spans="1:8">
-      <c r="A108" s="6"/>
+      <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="5"/>
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
       <c r="G108" s="4"/>
-      <c r="H108" s="5"/>
+      <c r="H108" s="4"/>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="4"/>
@@ -2590,28 +2648,28 @@
       <c r="H109" s="4"/>
     </row>
     <row r="110" spans="1:8">
-      <c r="A110" s="4"/>
+      <c r="A110" s="6"/>
       <c r="B110" s="4"/>
       <c r="C110" s="5"/>
       <c r="D110" s="4"/>
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
       <c r="G110" s="4"/>
-      <c r="H110" s="4"/>
+      <c r="H110" s="5"/>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="6"/>
+      <c r="A111" s="4"/>
       <c r="B111" s="4"/>
-      <c r="C111" s="5"/>
       <c r="D111" s="4"/>
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
       <c r="G111" s="4"/>
-      <c r="H111" s="5"/>
+      <c r="H111" s="4"/>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
+      <c r="C112" s="5"/>
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
@@ -2619,24 +2677,24 @@
       <c r="H112" s="4"/>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" s="4"/>
+      <c r="A113" s="6"/>
       <c r="B113" s="4"/>
       <c r="C113" s="5"/>
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
       <c r="G113" s="4"/>
-      <c r="H113" s="4"/>
+      <c r="H113" s="5"/>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="6"/>
+      <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="5"/>
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
-      <c r="H114" s="5"/>
+      <c r="H114" s="4"/>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="4"/>
@@ -2649,24 +2707,24 @@
       <c r="H115" s="4"/>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="4"/>
+      <c r="A116" s="6"/>
       <c r="B116" s="4"/>
       <c r="C116" s="5"/>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
       <c r="G116" s="4"/>
-      <c r="H116" s="4"/>
+      <c r="H116" s="5"/>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" s="6"/>
+      <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="5"/>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
       <c r="G117" s="4"/>
-      <c r="H117" s="5"/>
+      <c r="H117" s="4"/>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="4"/>
@@ -2679,24 +2737,24 @@
       <c r="H118" s="4"/>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="4"/>
+      <c r="A119" s="6"/>
       <c r="B119" s="4"/>
       <c r="C119" s="5"/>
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
       <c r="G119" s="4"/>
-      <c r="H119" s="4"/>
+      <c r="H119" s="5"/>
     </row>
     <row r="120" spans="1:8">
-      <c r="A120" s="6"/>
+      <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="5"/>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
       <c r="F120" s="4"/>
       <c r="G120" s="4"/>
-      <c r="H120" s="5"/>
+      <c r="H120" s="4"/>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="4"/>
@@ -2709,24 +2767,24 @@
       <c r="H121" s="4"/>
     </row>
     <row r="122" spans="1:8">
-      <c r="A122" s="4"/>
+      <c r="A122" s="6"/>
       <c r="B122" s="4"/>
       <c r="C122" s="5"/>
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
       <c r="F122" s="4"/>
       <c r="G122" s="4"/>
-      <c r="H122" s="4"/>
+      <c r="H122" s="5"/>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" s="6"/>
+      <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="5"/>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
       <c r="F123" s="4"/>
       <c r="G123" s="4"/>
-      <c r="H123" s="5"/>
+      <c r="H123" s="4"/>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="4"/>
@@ -2739,24 +2797,24 @@
       <c r="H124" s="4"/>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="4"/>
+      <c r="A125" s="6"/>
       <c r="B125" s="4"/>
       <c r="C125" s="5"/>
       <c r="D125" s="4"/>
-      <c r="E125" s="4"/>
+      <c r="E125" s="5"/>
       <c r="F125" s="4"/>
       <c r="G125" s="4"/>
-      <c r="H125" s="4"/>
+      <c r="H125" s="5"/>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" s="6"/>
+      <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="5"/>
       <c r="D126" s="4"/>
-      <c r="E126" s="5"/>
+      <c r="E126" s="4"/>
       <c r="F126" s="4"/>
       <c r="G126" s="4"/>
-      <c r="H126" s="5"/>
+      <c r="H126" s="4"/>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="4"/>
@@ -2769,24 +2827,24 @@
       <c r="H127" s="4"/>
     </row>
     <row r="128" spans="1:8">
-      <c r="A128" s="4"/>
+      <c r="A128" s="6"/>
       <c r="B128" s="4"/>
       <c r="C128" s="5"/>
       <c r="D128" s="4"/>
-      <c r="E128" s="4"/>
+      <c r="E128" s="5"/>
       <c r="F128" s="4"/>
       <c r="G128" s="4"/>
-      <c r="H128" s="4"/>
+      <c r="H128" s="5"/>
     </row>
     <row r="129" spans="1:8">
-      <c r="A129" s="6"/>
+      <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="5"/>
       <c r="D129" s="4"/>
-      <c r="E129" s="5"/>
+      <c r="E129" s="4"/>
       <c r="F129" s="4"/>
       <c r="G129" s="4"/>
-      <c r="H129" s="5"/>
+      <c r="H129" s="4"/>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="4"/>
@@ -2799,24 +2857,24 @@
       <c r="H130" s="4"/>
     </row>
     <row r="131" spans="1:8">
-      <c r="A131" s="4"/>
+      <c r="A131" s="6"/>
       <c r="B131" s="4"/>
       <c r="C131" s="5"/>
       <c r="D131" s="4"/>
-      <c r="E131" s="4"/>
+      <c r="E131" s="5"/>
       <c r="F131" s="4"/>
       <c r="G131" s="4"/>
-      <c r="H131" s="4"/>
+      <c r="H131" s="5"/>
     </row>
     <row r="132" spans="1:8">
-      <c r="A132" s="6"/>
+      <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="5"/>
       <c r="D132" s="4"/>
-      <c r="E132" s="5"/>
+      <c r="E132" s="4"/>
       <c r="F132" s="4"/>
       <c r="G132" s="4"/>
-      <c r="H132" s="5"/>
+      <c r="H132" s="4"/>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="4"/>
@@ -2829,24 +2887,24 @@
       <c r="H133" s="4"/>
     </row>
     <row r="134" spans="1:8">
-      <c r="A134" s="4"/>
+      <c r="A134" s="6"/>
       <c r="B134" s="4"/>
       <c r="C134" s="5"/>
       <c r="D134" s="4"/>
-      <c r="E134" s="4"/>
+      <c r="E134" s="5"/>
       <c r="F134" s="4"/>
       <c r="G134" s="4"/>
-      <c r="H134" s="4"/>
+      <c r="H134" s="5"/>
     </row>
     <row r="135" spans="1:8">
-      <c r="A135" s="6"/>
+      <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="5"/>
       <c r="D135" s="4"/>
-      <c r="E135" s="5"/>
+      <c r="E135" s="4"/>
       <c r="F135" s="4"/>
       <c r="G135" s="4"/>
-      <c r="H135" s="5"/>
+      <c r="H135" s="4"/>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="4"/>
@@ -2859,24 +2917,24 @@
       <c r="H136" s="4"/>
     </row>
     <row r="137" spans="1:8">
-      <c r="A137" s="4"/>
+      <c r="A137" s="6"/>
       <c r="B137" s="4"/>
       <c r="C137" s="5"/>
       <c r="D137" s="4"/>
-      <c r="E137" s="4"/>
+      <c r="E137" s="5"/>
       <c r="F137" s="4"/>
       <c r="G137" s="4"/>
-      <c r="H137" s="4"/>
+      <c r="H137" s="5"/>
     </row>
     <row r="138" spans="1:8">
-      <c r="A138" s="6"/>
+      <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="5"/>
       <c r="D138" s="4"/>
-      <c r="E138" s="5"/>
+      <c r="E138" s="4"/>
       <c r="F138" s="4"/>
       <c r="G138" s="4"/>
-      <c r="H138" s="5"/>
+      <c r="H138" s="4"/>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="4"/>
@@ -2889,51 +2947,51 @@
       <c r="H139" s="4"/>
     </row>
     <row r="140" spans="1:8">
-      <c r="A140" s="4"/>
+      <c r="A140" s="6"/>
       <c r="B140" s="4"/>
       <c r="C140" s="5"/>
       <c r="D140" s="4"/>
-      <c r="E140" s="4"/>
+      <c r="E140" s="5"/>
       <c r="F140" s="4"/>
       <c r="G140" s="4"/>
-      <c r="H140" s="4"/>
+      <c r="H140" s="5"/>
     </row>
     <row r="141" spans="1:8">
-      <c r="A141" s="6"/>
+      <c r="A141" s="4"/>
       <c r="B141" s="4"/>
-      <c r="C141" s="5"/>
-      <c r="D141" s="4"/>
-      <c r="E141" s="5"/>
-      <c r="F141" s="4"/>
+      <c r="C141" s="4"/>
       <c r="G141" s="4"/>
-      <c r="H141" s="5"/>
+      <c r="H141" s="4"/>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
-      <c r="C142" s="4"/>
+      <c r="C142" s="5"/>
+      <c r="D142" s="4"/>
+      <c r="E142" s="4"/>
+      <c r="F142" s="4"/>
       <c r="G142" s="4"/>
       <c r="H142" s="4"/>
     </row>
     <row r="143" spans="1:8">
-      <c r="A143" s="4"/>
+      <c r="A143" s="6"/>
       <c r="B143" s="4"/>
       <c r="C143" s="5"/>
       <c r="D143" s="4"/>
-      <c r="E143" s="4"/>
+      <c r="E143" s="5"/>
       <c r="F143" s="4"/>
       <c r="G143" s="4"/>
-      <c r="H143" s="4"/>
+      <c r="H143" s="5"/>
     </row>
     <row r="144" spans="1:8">
-      <c r="A144" s="6"/>
+      <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="5"/>
       <c r="D144" s="4"/>
-      <c r="E144" s="5"/>
+      <c r="E144" s="4"/>
       <c r="F144" s="4"/>
       <c r="G144" s="4"/>
-      <c r="H144" s="5"/>
+      <c r="H144" s="4"/>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="4"/>
@@ -2946,21 +3004,21 @@
       <c r="H145" s="4"/>
     </row>
     <row r="146" spans="1:8">
-      <c r="A146" s="4"/>
+      <c r="A146" s="6"/>
       <c r="B146" s="4"/>
       <c r="C146" s="5"/>
       <c r="D146" s="4"/>
-      <c r="E146" s="4"/>
+      <c r="E146" s="5"/>
       <c r="F146" s="4"/>
       <c r="G146" s="4"/>
-      <c r="H146" s="4"/>
+      <c r="H146" s="5"/>
     </row>
     <row r="147" spans="1:8">
-      <c r="A147" s="6"/>
+      <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="5"/>
       <c r="D147" s="4"/>
-      <c r="E147" s="5"/>
+      <c r="E147" s="4"/>
       <c r="F147" s="4"/>
       <c r="G147" s="4"/>
       <c r="H147" s="5"/>
@@ -2976,21 +3034,21 @@
       <c r="H148" s="5"/>
     </row>
     <row r="149" spans="1:8">
-      <c r="A149" s="4"/>
+      <c r="A149" s="6"/>
       <c r="B149" s="4"/>
       <c r="C149" s="5"/>
       <c r="D149" s="4"/>
-      <c r="E149" s="4"/>
+      <c r="E149" s="5"/>
       <c r="F149" s="4"/>
       <c r="G149" s="4"/>
       <c r="H149" s="5"/>
     </row>
     <row r="150" spans="1:8">
-      <c r="A150" s="6"/>
+      <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="5"/>
       <c r="D150" s="4"/>
-      <c r="E150" s="5"/>
+      <c r="E150" s="4"/>
       <c r="F150" s="4"/>
       <c r="G150" s="4"/>
       <c r="H150" s="5"/>
@@ -3006,21 +3064,21 @@
       <c r="H151" s="5"/>
     </row>
     <row r="152" spans="1:8">
-      <c r="A152" s="4"/>
+      <c r="A152" s="6"/>
       <c r="B152" s="4"/>
       <c r="C152" s="5"/>
       <c r="D152" s="4"/>
-      <c r="E152" s="4"/>
+      <c r="E152" s="5"/>
       <c r="F152" s="4"/>
       <c r="G152" s="4"/>
       <c r="H152" s="5"/>
     </row>
     <row r="153" spans="1:8">
-      <c r="A153" s="6"/>
+      <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="5"/>
       <c r="D153" s="4"/>
-      <c r="E153" s="5"/>
+      <c r="E153" s="4"/>
       <c r="F153" s="4"/>
       <c r="G153" s="4"/>
       <c r="H153" s="5"/>
@@ -3036,7 +3094,7 @@
       <c r="H154" s="5"/>
     </row>
     <row r="155" spans="1:8">
-      <c r="A155" s="4"/>
+      <c r="A155" s="6"/>
       <c r="B155" s="4"/>
       <c r="C155" s="5"/>
       <c r="D155" s="4"/>
@@ -3046,7 +3104,7 @@
       <c r="H155" s="5"/>
     </row>
     <row r="156" spans="1:8">
-      <c r="A156" s="6"/>
+      <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="5"/>
       <c r="D156" s="4"/>
@@ -3066,21 +3124,21 @@
       <c r="H157" s="5"/>
     </row>
     <row r="158" spans="1:8">
-      <c r="A158" s="4"/>
+      <c r="A158" s="6"/>
       <c r="B158" s="4"/>
       <c r="C158" s="5"/>
       <c r="D158" s="4"/>
-      <c r="E158" s="4"/>
+      <c r="E158" s="5"/>
       <c r="F158" s="4"/>
       <c r="G158" s="4"/>
       <c r="H158" s="5"/>
     </row>
     <row r="159" spans="1:8">
-      <c r="A159" s="6"/>
+      <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="5"/>
       <c r="D159" s="4"/>
-      <c r="E159" s="5"/>
+      <c r="E159" s="4"/>
       <c r="F159" s="4"/>
       <c r="G159" s="4"/>
       <c r="H159" s="5"/>
@@ -3096,21 +3154,21 @@
       <c r="H160" s="5"/>
     </row>
     <row r="161" spans="1:8">
-      <c r="A161" s="4"/>
+      <c r="A161" s="6"/>
       <c r="B161" s="4"/>
       <c r="C161" s="5"/>
       <c r="D161" s="4"/>
-      <c r="E161" s="4"/>
+      <c r="E161" s="5"/>
       <c r="F161" s="4"/>
       <c r="G161" s="4"/>
       <c r="H161" s="5"/>
     </row>
     <row r="162" spans="1:8">
-      <c r="A162" s="6"/>
+      <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="5"/>
       <c r="D162" s="4"/>
-      <c r="E162" s="5"/>
+      <c r="E162" s="4"/>
       <c r="F162" s="4"/>
       <c r="G162" s="4"/>
       <c r="H162" s="5"/>
@@ -3126,21 +3184,21 @@
       <c r="H163" s="5"/>
     </row>
     <row r="164" spans="1:8">
-      <c r="A164" s="4"/>
+      <c r="A164" s="6"/>
       <c r="B164" s="4"/>
       <c r="C164" s="5"/>
       <c r="D164" s="4"/>
-      <c r="E164" s="4"/>
+      <c r="E164" s="5"/>
       <c r="F164" s="4"/>
       <c r="G164" s="4"/>
       <c r="H164" s="5"/>
     </row>
     <row r="165" spans="1:8">
-      <c r="A165" s="6"/>
+      <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="5"/>
       <c r="D165" s="4"/>
-      <c r="E165" s="5"/>
+      <c r="E165" s="4"/>
       <c r="F165" s="4"/>
       <c r="G165" s="4"/>
       <c r="H165" s="5"/>
@@ -3156,21 +3214,21 @@
       <c r="H166" s="5"/>
     </row>
     <row r="167" spans="1:8">
-      <c r="A167" s="4"/>
+      <c r="A167" s="6"/>
       <c r="B167" s="4"/>
       <c r="C167" s="5"/>
       <c r="D167" s="4"/>
-      <c r="E167" s="4"/>
+      <c r="E167" s="5"/>
       <c r="F167" s="4"/>
       <c r="G167" s="4"/>
       <c r="H167" s="5"/>
     </row>
     <row r="168" spans="1:8">
-      <c r="A168" s="6"/>
+      <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="5"/>
       <c r="D168" s="4"/>
-      <c r="E168" s="5"/>
+      <c r="E168" s="4"/>
       <c r="F168" s="4"/>
       <c r="G168" s="4"/>
       <c r="H168" s="5"/>
@@ -3186,21 +3244,21 @@
       <c r="H169" s="5"/>
     </row>
     <row r="170" spans="1:8">
-      <c r="A170" s="4"/>
+      <c r="A170" s="6"/>
       <c r="B170" s="4"/>
       <c r="C170" s="5"/>
       <c r="D170" s="4"/>
-      <c r="E170" s="4"/>
+      <c r="E170" s="5"/>
       <c r="F170" s="4"/>
       <c r="G170" s="4"/>
       <c r="H170" s="5"/>
     </row>
     <row r="171" spans="1:8">
-      <c r="A171" s="6"/>
+      <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="5"/>
       <c r="D171" s="4"/>
-      <c r="E171" s="5"/>
+      <c r="E171" s="4"/>
       <c r="F171" s="4"/>
       <c r="G171" s="4"/>
       <c r="H171" s="5"/>
@@ -3216,21 +3274,21 @@
       <c r="H172" s="5"/>
     </row>
     <row r="173" spans="1:8">
-      <c r="A173" s="4"/>
+      <c r="A173" s="6"/>
       <c r="B173" s="4"/>
       <c r="C173" s="5"/>
       <c r="D173" s="4"/>
-      <c r="E173" s="4"/>
+      <c r="E173" s="5"/>
       <c r="F173" s="4"/>
       <c r="G173" s="4"/>
       <c r="H173" s="5"/>
     </row>
     <row r="174" spans="1:8">
-      <c r="A174" s="6"/>
+      <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="5"/>
       <c r="D174" s="4"/>
-      <c r="E174" s="5"/>
+      <c r="E174" s="4"/>
       <c r="F174" s="4"/>
       <c r="G174" s="4"/>
       <c r="H174" s="5"/>
@@ -3246,21 +3304,20 @@
       <c r="H175" s="5"/>
     </row>
     <row r="176" spans="1:8">
-      <c r="A176" s="4"/>
+      <c r="A176" s="6"/>
       <c r="B176" s="4"/>
       <c r="C176" s="5"/>
       <c r="D176" s="4"/>
-      <c r="E176" s="4"/>
+      <c r="E176" s="5"/>
       <c r="F176" s="4"/>
       <c r="G176" s="4"/>
       <c r="H176" s="5"/>
     </row>
     <row r="177" spans="1:8">
-      <c r="A177" s="6"/>
+      <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="5"/>
-      <c r="D177" s="4"/>
-      <c r="E177" s="5"/>
+      <c r="E177" s="4"/>
       <c r="F177" s="4"/>
       <c r="G177" s="4"/>
       <c r="H177" s="5"/>
@@ -3269,27 +3326,28 @@
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="5"/>
+      <c r="D178" s="4"/>
       <c r="E178" s="4"/>
       <c r="F178" s="4"/>
       <c r="G178" s="4"/>
       <c r="H178" s="5"/>
     </row>
     <row r="179" spans="1:8">
-      <c r="A179" s="4"/>
+      <c r="A179" s="6"/>
       <c r="B179" s="4"/>
       <c r="C179" s="5"/>
       <c r="D179" s="4"/>
-      <c r="E179" s="4"/>
+      <c r="E179" s="5"/>
       <c r="F179" s="4"/>
       <c r="G179" s="4"/>
       <c r="H179" s="5"/>
     </row>
     <row r="180" spans="1:8">
-      <c r="A180" s="6"/>
+      <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="5"/>
       <c r="D180" s="4"/>
-      <c r="E180" s="5"/>
+      <c r="E180" s="4"/>
       <c r="F180" s="4"/>
       <c r="G180" s="4"/>
       <c r="H180" s="5"/>
@@ -3303,16 +3361,6 @@
       <c r="F181" s="4"/>
       <c r="G181" s="4"/>
       <c r="H181" s="5"/>
-    </row>
-    <row r="182" spans="1:8">
-      <c r="A182" s="4"/>
-      <c r="B182" s="4"/>
-      <c r="C182" s="5"/>
-      <c r="D182" s="4"/>
-      <c r="E182" s="4"/>
-      <c r="F182" s="4"/>
-      <c r="G182" s="4"/>
-      <c r="H182" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="120">
@@ -3329,53 +3377,53 @@
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="A35:A37"/>
     <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="A60:A62"/>
-    <mergeCell ref="A63:A65"/>
-    <mergeCell ref="A66:A68"/>
-    <mergeCell ref="A69:A71"/>
-    <mergeCell ref="A72:A74"/>
-    <mergeCell ref="A75:A77"/>
-    <mergeCell ref="A78:A80"/>
-    <mergeCell ref="A81:A83"/>
-    <mergeCell ref="A84:A86"/>
-    <mergeCell ref="A87:A89"/>
-    <mergeCell ref="A90:A92"/>
-    <mergeCell ref="A93:A95"/>
-    <mergeCell ref="A96:A98"/>
-    <mergeCell ref="A99:A101"/>
-    <mergeCell ref="A102:A104"/>
-    <mergeCell ref="A105:A107"/>
-    <mergeCell ref="A108:A110"/>
-    <mergeCell ref="A111:A113"/>
-    <mergeCell ref="A114:A116"/>
-    <mergeCell ref="A117:A119"/>
-    <mergeCell ref="A120:A122"/>
-    <mergeCell ref="A123:A125"/>
-    <mergeCell ref="A126:A128"/>
-    <mergeCell ref="A129:A131"/>
-    <mergeCell ref="A132:A134"/>
-    <mergeCell ref="A135:A137"/>
-    <mergeCell ref="A138:A140"/>
-    <mergeCell ref="A141:A143"/>
-    <mergeCell ref="A144:A146"/>
-    <mergeCell ref="A147:A149"/>
-    <mergeCell ref="A150:A152"/>
-    <mergeCell ref="A153:A155"/>
-    <mergeCell ref="A156:A158"/>
-    <mergeCell ref="A159:A161"/>
-    <mergeCell ref="A162:A164"/>
-    <mergeCell ref="A165:A167"/>
-    <mergeCell ref="A168:A170"/>
-    <mergeCell ref="A171:A173"/>
-    <mergeCell ref="A174:A176"/>
-    <mergeCell ref="A177:A179"/>
-    <mergeCell ref="A180:A182"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A112"/>
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="A116:A118"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="A122:A124"/>
+    <mergeCell ref="A125:A127"/>
+    <mergeCell ref="A128:A130"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="A134:A136"/>
+    <mergeCell ref="A137:A139"/>
+    <mergeCell ref="A140:A142"/>
+    <mergeCell ref="A143:A145"/>
+    <mergeCell ref="A146:A148"/>
+    <mergeCell ref="A149:A151"/>
+    <mergeCell ref="A152:A154"/>
+    <mergeCell ref="A155:A157"/>
+    <mergeCell ref="A158:A160"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="A164:A166"/>
+    <mergeCell ref="A167:A169"/>
+    <mergeCell ref="A170:A172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A179:A181"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="H5:H7"/>
     <mergeCell ref="H8:H10"/>
@@ -3389,53 +3437,53 @@
     <mergeCell ref="H32:H34"/>
     <mergeCell ref="H35:H37"/>
     <mergeCell ref="H38:H40"/>
-    <mergeCell ref="H42:H44"/>
-    <mergeCell ref="H45:H47"/>
-    <mergeCell ref="H48:H50"/>
-    <mergeCell ref="H51:H53"/>
-    <mergeCell ref="H54:H56"/>
-    <mergeCell ref="H57:H59"/>
-    <mergeCell ref="H60:H62"/>
-    <mergeCell ref="H63:H65"/>
-    <mergeCell ref="H66:H68"/>
-    <mergeCell ref="H69:H71"/>
-    <mergeCell ref="H72:H74"/>
-    <mergeCell ref="H75:H77"/>
-    <mergeCell ref="H78:H80"/>
-    <mergeCell ref="H81:H83"/>
-    <mergeCell ref="H84:H86"/>
-    <mergeCell ref="H87:H89"/>
-    <mergeCell ref="H90:H92"/>
-    <mergeCell ref="H93:H95"/>
-    <mergeCell ref="H96:H98"/>
-    <mergeCell ref="H99:H101"/>
-    <mergeCell ref="H102:H104"/>
-    <mergeCell ref="H105:H107"/>
-    <mergeCell ref="H108:H110"/>
-    <mergeCell ref="H111:H113"/>
-    <mergeCell ref="H114:H116"/>
-    <mergeCell ref="H117:H119"/>
-    <mergeCell ref="H120:H122"/>
-    <mergeCell ref="H123:H125"/>
-    <mergeCell ref="H126:H128"/>
-    <mergeCell ref="H129:H131"/>
-    <mergeCell ref="H132:H134"/>
-    <mergeCell ref="H135:H137"/>
-    <mergeCell ref="H138:H140"/>
-    <mergeCell ref="H141:H143"/>
-    <mergeCell ref="H144:H146"/>
-    <mergeCell ref="H147:H149"/>
-    <mergeCell ref="H150:H152"/>
-    <mergeCell ref="H153:H155"/>
-    <mergeCell ref="H156:H158"/>
-    <mergeCell ref="H159:H161"/>
-    <mergeCell ref="H162:H164"/>
-    <mergeCell ref="H165:H167"/>
-    <mergeCell ref="H168:H170"/>
-    <mergeCell ref="H171:H173"/>
-    <mergeCell ref="H174:H176"/>
-    <mergeCell ref="H177:H179"/>
-    <mergeCell ref="H180:H182"/>
+    <mergeCell ref="H41:H43"/>
+    <mergeCell ref="H44:H46"/>
+    <mergeCell ref="H47:H49"/>
+    <mergeCell ref="H50:H52"/>
+    <mergeCell ref="H53:H55"/>
+    <mergeCell ref="H56:H58"/>
+    <mergeCell ref="H59:H61"/>
+    <mergeCell ref="H62:H64"/>
+    <mergeCell ref="H65:H67"/>
+    <mergeCell ref="H68:H70"/>
+    <mergeCell ref="H71:H73"/>
+    <mergeCell ref="H74:H76"/>
+    <mergeCell ref="H77:H79"/>
+    <mergeCell ref="H80:H82"/>
+    <mergeCell ref="H83:H85"/>
+    <mergeCell ref="H86:H88"/>
+    <mergeCell ref="H89:H91"/>
+    <mergeCell ref="H92:H94"/>
+    <mergeCell ref="H95:H97"/>
+    <mergeCell ref="H98:H100"/>
+    <mergeCell ref="H101:H103"/>
+    <mergeCell ref="H104:H106"/>
+    <mergeCell ref="H107:H109"/>
+    <mergeCell ref="H110:H112"/>
+    <mergeCell ref="H113:H115"/>
+    <mergeCell ref="H116:H118"/>
+    <mergeCell ref="H119:H121"/>
+    <mergeCell ref="H122:H124"/>
+    <mergeCell ref="H125:H127"/>
+    <mergeCell ref="H128:H130"/>
+    <mergeCell ref="H131:H133"/>
+    <mergeCell ref="H134:H136"/>
+    <mergeCell ref="H137:H139"/>
+    <mergeCell ref="H140:H142"/>
+    <mergeCell ref="H143:H145"/>
+    <mergeCell ref="H146:H148"/>
+    <mergeCell ref="H149:H151"/>
+    <mergeCell ref="H152:H154"/>
+    <mergeCell ref="H155:H157"/>
+    <mergeCell ref="H158:H160"/>
+    <mergeCell ref="H161:H163"/>
+    <mergeCell ref="H164:H166"/>
+    <mergeCell ref="H167:H169"/>
+    <mergeCell ref="H170:H172"/>
+    <mergeCell ref="H173:H175"/>
+    <mergeCell ref="H176:H178"/>
+    <mergeCell ref="H179:H181"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/2026年下半年减肥记录每一天.xlsx
+++ b/2026年下半年减肥记录每一天.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="31545" windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="100">
   <si>
     <t>时间</t>
   </si>
@@ -295,6 +295,57 @@
   <si>
     <t>目前83.75kg
 明天争取到83.6kg，加油</t>
+  </si>
+  <si>
+    <t>鸡腿1 + 鸡蛋</t>
+  </si>
+  <si>
+    <t>杂粮饭 + 黑麦面条</t>
+  </si>
+  <si>
+    <t>快餐</t>
+  </si>
+  <si>
+    <t>鸡排 + 鱼肉</t>
+  </si>
+  <si>
+    <t>黄瓜 + 白菜</t>
+  </si>
+  <si>
+    <t>一碗白菜 + 小馒头2 + 玉米2 + 鸡蛋2 + 鸡杂</t>
+  </si>
+  <si>
+    <t>鸡蛋2 + 鸡杂</t>
+  </si>
+  <si>
+    <t>白馒头 + 玉米</t>
+  </si>
+  <si>
+    <t>目前83.70kg
+明天争取到83.6kg，加油
+一定能达标的。</t>
+  </si>
+  <si>
+    <t>大鸡腿2 + 混合蔬菜 + 馒头 玉米</t>
+  </si>
+  <si>
+    <t>大鸡腿2</t>
+  </si>
+  <si>
+    <t>蔬菜冒菜</t>
+  </si>
+  <si>
+    <t>过午不食</t>
+  </si>
+  <si>
+    <t>没吃</t>
+  </si>
+  <si>
+    <t>周六早上节食</t>
+  </si>
+  <si>
+    <t>目前82.90kg
+本周争取到83.6kg</t>
   </si>
 </sst>
 </file>
@@ -1256,7 +1307,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H181"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="18.75" style="1" customWidth="1"/>
@@ -1832,7 +1883,7 @@
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="4" t="s">
         <v>82</v>
       </c>
       <c r="H31" s="4"/>
@@ -1871,10 +1922,18 @@
       <c r="C33" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
+      <c r="D33" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8">
@@ -1882,61 +1941,113 @@
       <c r="B34" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="1"/>
+      <c r="C34" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="3">
         <v>46318</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="5"/>
+      <c r="B35" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="6"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
+      <c r="B36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="6"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
+      <c r="B37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
-      <c r="G37" s="1"/>
+      <c r="G37" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="3">
-        <v>46321</v>
-      </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="5"/>
+        <v>46319</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>97</v>
+      </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="5"/>
+      <c r="G38" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="6"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="5"/>
+      <c r="B39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -1945,8 +2056,10 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="6"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="5"/>
+      <c r="B40" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -1955,10 +2068,10 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="3">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="B41" s="4"/>
-      <c r="C41" s="5"/>
+      <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
@@ -1968,7 +2081,7 @@
     <row r="42" spans="1:8">
       <c r="A42" s="6"/>
       <c r="B42" s="4"/>
-      <c r="C42" s="5"/>
+      <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
@@ -1978,7 +2091,7 @@
     <row r="43" spans="1:8">
       <c r="A43" s="6"/>
       <c r="B43" s="4"/>
-      <c r="C43" s="5"/>
+      <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
@@ -1987,10 +2100,10 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="3">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="B44" s="4"/>
-      <c r="C44" s="5"/>
+      <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
@@ -2000,7 +2113,7 @@
     <row r="45" spans="1:8">
       <c r="A45" s="6"/>
       <c r="B45" s="4"/>
-      <c r="C45" s="5"/>
+      <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
@@ -2010,7 +2123,7 @@
     <row r="46" spans="1:8">
       <c r="A46" s="6"/>
       <c r="B46" s="4"/>
-      <c r="C46" s="5"/>
+      <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
@@ -2018,9 +2131,11 @@
       <c r="H46" s="4"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="6"/>
+      <c r="A47" s="3">
+        <v>46323</v>
+      </c>
       <c r="B47" s="4"/>
-      <c r="C47" s="5"/>
+      <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
@@ -2028,7 +2143,7 @@
       <c r="H47" s="5"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="4"/>
+      <c r="A48" s="6"/>
       <c r="B48" s="4"/>
       <c r="C48" s="5"/>
       <c r="D48" s="4"/>
@@ -2038,7 +2153,7 @@
       <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="4"/>
+      <c r="A49" s="6"/>
       <c r="B49" s="4"/>
       <c r="C49" s="5"/>
       <c r="D49" s="4"/>
@@ -2614,7 +2729,7 @@
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
-      <c r="G106" s="5"/>
+      <c r="G106" s="4"/>
       <c r="H106" s="4"/>
     </row>
     <row r="107" spans="1:8">
@@ -2644,7 +2759,7 @@
       <c r="D109" s="4"/>
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
-      <c r="G109" s="4"/>
+      <c r="G109" s="5"/>
       <c r="H109" s="4"/>
     </row>
     <row r="110" spans="1:8">
@@ -2660,6 +2775,7 @@
     <row r="111" spans="1:8">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
+      <c r="C111" s="5"/>
       <c r="D111" s="4"/>
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
@@ -2689,7 +2805,6 @@
     <row r="114" spans="1:8">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
-      <c r="C114" s="5"/>
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
@@ -2801,7 +2916,7 @@
       <c r="B125" s="4"/>
       <c r="C125" s="5"/>
       <c r="D125" s="4"/>
-      <c r="E125" s="5"/>
+      <c r="E125" s="4"/>
       <c r="F125" s="4"/>
       <c r="G125" s="4"/>
       <c r="H125" s="5"/>
@@ -2959,7 +3074,10 @@
     <row r="141" spans="1:8">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
-      <c r="C141" s="4"/>
+      <c r="C141" s="5"/>
+      <c r="D141" s="4"/>
+      <c r="E141" s="4"/>
+      <c r="F141" s="4"/>
       <c r="G141" s="4"/>
       <c r="H141" s="4"/>
     </row>
@@ -2986,10 +3104,7 @@
     <row r="144" spans="1:8">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
-      <c r="C144" s="5"/>
-      <c r="D144" s="4"/>
-      <c r="E144" s="4"/>
-      <c r="F144" s="4"/>
+      <c r="C144" s="4"/>
       <c r="G144" s="4"/>
       <c r="H144" s="4"/>
     </row>
@@ -3021,7 +3136,7 @@
       <c r="E147" s="4"/>
       <c r="F147" s="4"/>
       <c r="G147" s="4"/>
-      <c r="H147" s="5"/>
+      <c r="H147" s="4"/>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="4"/>
@@ -3031,7 +3146,7 @@
       <c r="E148" s="4"/>
       <c r="F148" s="4"/>
       <c r="G148" s="4"/>
-      <c r="H148" s="5"/>
+      <c r="H148" s="4"/>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="6"/>
@@ -3098,7 +3213,7 @@
       <c r="B155" s="4"/>
       <c r="C155" s="5"/>
       <c r="D155" s="4"/>
-      <c r="E155" s="4"/>
+      <c r="E155" s="5"/>
       <c r="F155" s="4"/>
       <c r="G155" s="4"/>
       <c r="H155" s="5"/>
@@ -3128,7 +3243,7 @@
       <c r="B158" s="4"/>
       <c r="C158" s="5"/>
       <c r="D158" s="4"/>
-      <c r="E158" s="5"/>
+      <c r="E158" s="4"/>
       <c r="F158" s="4"/>
       <c r="G158" s="4"/>
       <c r="H158" s="5"/>
@@ -3317,6 +3432,7 @@
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="5"/>
+      <c r="D177" s="4"/>
       <c r="E177" s="4"/>
       <c r="F177" s="4"/>
       <c r="G177" s="4"/>
@@ -3346,7 +3462,6 @@
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="5"/>
-      <c r="D180" s="4"/>
       <c r="E180" s="4"/>
       <c r="F180" s="4"/>
       <c r="G180" s="4"/>
@@ -3362,8 +3477,38 @@
       <c r="G181" s="4"/>
       <c r="H181" s="5"/>
     </row>
+    <row r="182" spans="1:8">
+      <c r="A182" s="6"/>
+      <c r="B182" s="4"/>
+      <c r="C182" s="5"/>
+      <c r="D182" s="4"/>
+      <c r="E182" s="5"/>
+      <c r="F182" s="4"/>
+      <c r="G182" s="4"/>
+      <c r="H182" s="5"/>
+    </row>
+    <row r="183" spans="1:8">
+      <c r="A183" s="4"/>
+      <c r="B183" s="4"/>
+      <c r="C183" s="5"/>
+      <c r="D183" s="4"/>
+      <c r="E183" s="4"/>
+      <c r="F183" s="4"/>
+      <c r="G183" s="4"/>
+      <c r="H183" s="5"/>
+    </row>
+    <row r="184" spans="1:8">
+      <c r="A184" s="4"/>
+      <c r="B184" s="4"/>
+      <c r="C184" s="5"/>
+      <c r="D184" s="4"/>
+      <c r="E184" s="4"/>
+      <c r="F184" s="4"/>
+      <c r="G184" s="4"/>
+      <c r="H184" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="120">
+  <mergeCells count="122">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A8:A10"/>
@@ -3424,6 +3569,7 @@
     <mergeCell ref="A173:A175"/>
     <mergeCell ref="A176:A178"/>
     <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A182:A184"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="H5:H7"/>
     <mergeCell ref="H8:H10"/>
@@ -3484,6 +3630,7 @@
     <mergeCell ref="H173:H175"/>
     <mergeCell ref="H176:H178"/>
     <mergeCell ref="H179:H181"/>
+    <mergeCell ref="H182:H184"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/2026年下半年减肥记录每一天.xlsx
+++ b/2026年下半年减肥记录每一天.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="31545" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="107">
   <si>
     <t>时间</t>
   </si>
@@ -338,14 +338,36 @@
     <t>过午不食</t>
   </si>
   <si>
-    <t>没吃</t>
-  </si>
-  <si>
-    <t>周六早上节食</t>
-  </si>
-  <si>
     <t>目前82.90kg
 本周争取到83.6kg</t>
+  </si>
+  <si>
+    <t>驴肉 + 土豆 + 混合蔬菜</t>
+  </si>
+  <si>
+    <t>驴肉</t>
+  </si>
+  <si>
+    <t>土豆</t>
+  </si>
+  <si>
+    <t>西红柿鸡蛋面</t>
+  </si>
+  <si>
+    <t>鸡蛋1</t>
+  </si>
+  <si>
+    <t>荞麦面</t>
+  </si>
+  <si>
+    <t>西红柿</t>
+  </si>
+  <si>
+    <t>卷饼 + 豆浆</t>
+  </si>
+  <si>
+    <t>目前83.00kg
+本周争取到82.0kg</t>
   </si>
 </sst>
 </file>
@@ -2024,22 +2046,18 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="3">
-        <v>46319</v>
+        <v>46322</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>97</v>
-      </c>
+      <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
-      <c r="G38" s="4" t="s">
-        <v>98</v>
-      </c>
+      <c r="G38" s="4"/>
       <c r="H38" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -2047,11 +2065,21 @@
       <c r="B39" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
+      <c r="C39" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8">
@@ -2059,28 +2087,46 @@
       <c r="B40" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
+      <c r="C40" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="3">
-        <v>46321</v>
-      </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
+        <v>46324</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>105</v>
+      </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="5"/>
+      <c r="G41" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="6"/>
-      <c r="B42" s="4"/>
+      <c r="B42" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -2090,7 +2136,9 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="6"/>
-      <c r="B43" s="4"/>
+      <c r="B43" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -2100,7 +2148,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="3">
-        <v>46322</v>
+        <v>46325</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -2132,7 +2180,7 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="3">
-        <v>46323</v>
+        <v>46326</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
